--- a/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>202</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.41508</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.68375</v>
-      </c>
-      <c r="I2" t="n">
-        <v>280</v>
-      </c>
-      <c r="J2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.41508</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.68375</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>SANTA TERESA</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.42242</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-75.69277</v>
-      </c>
-      <c r="I3" t="n">
-        <v>523</v>
-      </c>
-      <c r="J3" t="n">
-        <v>25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.42242</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-75.69277</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>30703 JOSE GUILLERMO OTERO</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.42492</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.69206</v>
-      </c>
-      <c r="I4" t="n">
-        <v>341</v>
-      </c>
-      <c r="J4" t="n">
-        <v>28</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.42492</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.69206</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>SAN RAMON</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.40887</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-75.68295000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1187</v>
-      </c>
-      <c r="J5" t="n">
-        <v>81</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.40887</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-75.68295</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>30708 ROSA DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.41904</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.69807</v>
-      </c>
-      <c r="I6" t="n">
-        <v>200</v>
-      </c>
-      <c r="J6" t="n">
-        <v>17</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.41904</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.69807</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>30711 WILHELM HOFMANN</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.41853</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-75.68477</v>
-      </c>
-      <c r="I7" t="n">
-        <v>357</v>
-      </c>
-      <c r="J7" t="n">
-        <v>23</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.41853</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-75.68477</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>31516 MARISCAL CASTILLA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.41546</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-75.68331999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>743</v>
-      </c>
-      <c r="J8" t="n">
-        <v>45</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.41546</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-75.68332</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>31517 ANGELA MORENO DE GALVEZ</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.4139</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.68608999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>407</v>
-      </c>
-      <c r="J9" t="n">
-        <v>25</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.4139</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.68609</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>31518 JOSE GALVEZ BARRENECHEA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.42145</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-75.69009</v>
-      </c>
-      <c r="I10" t="n">
-        <v>823</v>
-      </c>
-      <c r="J10" t="n">
-        <v>45</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.42145</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-75.69009</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>INDUSTRIAL 32</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.40837</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.68365</v>
-      </c>
-      <c r="I11" t="n">
-        <v>976</v>
-      </c>
-      <c r="J11" t="n">
-        <v>60</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.40837</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.68365</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>ANGELA MORENO DE GALVEZ</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.414197</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.685615</v>
-      </c>
-      <c r="I12" t="n">
-        <v>980</v>
-      </c>
-      <c r="J12" t="n">
-        <v>69</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.414197</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.685615</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.4173</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.67931</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1002</v>
-      </c>
-      <c r="J13" t="n">
-        <v>46</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.4173</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.67931</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.42046</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-75.69265</v>
-      </c>
-      <c r="I14" t="n">
-        <v>387</v>
-      </c>
-      <c r="J14" t="n">
-        <v>26</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.42046</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-75.69265</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>SANTA CLARA DE ASIS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-11.4163</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-75.69537</v>
-      </c>
-      <c r="I15" t="n">
-        <v>269</v>
-      </c>
-      <c r="J15" t="n">
-        <v>20</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-11.4163</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-75.69537</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>HUGO VELASQUEZ MACASSI</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-11.41605</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.68384</v>
-      </c>
-      <c r="I16" t="n">
-        <v>200</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-11.41605</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.68384</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>AGORA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.41741</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-75.68996</v>
-      </c>
-      <c r="I17" t="n">
-        <v>230</v>
-      </c>
-      <c r="J17" t="n">
-        <v>29</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.41741</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-75.68996</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.42182</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-75.68810000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>279</v>
-      </c>
-      <c r="J18" t="n">
-        <v>19</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.42182</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.6881</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>30731 SOR IRENE THERESE MC CORMACK</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.2657</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-75.6498</v>
-      </c>
-      <c r="I19" t="n">
-        <v>430</v>
-      </c>
-      <c r="J19" t="n">
-        <v>14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.2657</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-75.6498</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>30743 SAN ANTONIO DE PADUA / 717</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.295425</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-75.772823</v>
-      </c>
-      <c r="I20" t="n">
-        <v>221</v>
-      </c>
-      <c r="J20" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.295425</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-75.772823</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>ORION</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.41967</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-75.69092999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>291</v>
-      </c>
-      <c r="J21" t="n">
-        <v>19</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.41967</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-75.69093</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>FE Y ALEGRIA 67 MARIA INMACULADA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.41521</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-75.67847</v>
-      </c>
-      <c r="I22" t="n">
-        <v>366</v>
-      </c>
-      <c r="J22" t="n">
-        <v>23</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.41521</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-75.67847</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>NEWTON</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.43186</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-75.69118</v>
-      </c>
-      <c r="I23" t="n">
-        <v>427</v>
-      </c>
-      <c r="J23" t="n">
-        <v>15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.43186</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-75.69118</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>EINSTEIN</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.41969</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-75.69096</v>
-      </c>
-      <c r="I24" t="n">
-        <v>232</v>
-      </c>
-      <c r="J24" t="n">
-        <v>19</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.41969</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-75.69096</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>NUEVO HORIZONTE</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.42067</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-75.69427</v>
-      </c>
-      <c r="I25" t="n">
-        <v>234</v>
-      </c>
-      <c r="J25" t="n">
-        <v>19</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.42067</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-75.69427</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>PERUANO EUROPEO CELESTIN FREINET</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.40734</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-75.68237999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>200</v>
-      </c>
-      <c r="J26" t="n">
-        <v>19</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.40734</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-75.68238</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>SACO OLIVERO TARMA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-11.419918</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-75.68777</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-11.419918</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-75.68777</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>244480</t>
+          <t>911867</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>SACO OLIVERO TARMA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.41508</t>
+          <t>-11.419918</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.68375</t>
+          <t>-75.68777</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>244588</t>
+          <t>245272</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SANTA TERESA</t>
+          <t>HUGO VELASQUEZ MACASSI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.42242</t>
+          <t>-11.41605</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.69277</t>
+          <t>-75.68384</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>244606</t>
+          <t>246139</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30703 JOSE GUILLERMO OTERO</t>
+          <t>30731 SOR IRENE THERESE MC CORMACK</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.42492</t>
+          <t>-11.2657</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.69206</t>
+          <t>-75.6498</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>430</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>655037</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.40887</t>
+          <t>-11.43186</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.68295</t>
+          <t>-75.69118</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>427</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>244649</t>
+          <t>244480</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>30708 ROSA DE SANTA MARIA</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.41904</t>
+          <t>-11.41508</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.69807</t>
+          <t>-75.68375</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>280</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>244673</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30711 WILHELM HOFMANN</t>
+          <t>30708 ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.41853</t>
+          <t>-11.41904</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.68477</t>
+          <t>-75.69807</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>244951</t>
+          <t>246894</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31516 MARISCAL CASTILLA</t>
+          <t>30743 SAN ANTONIO DE PADUA / 717</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.41546</t>
+          <t>-11.295425</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.68332</t>
+          <t>-75.772823</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>244965</t>
+          <t>245465</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31517 ANGELA MORENO DE GALVEZ</t>
+          <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.4139</t>
+          <t>-11.42182</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.68609</t>
+          <t>-75.6881</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>244970</t>
+          <t>295361</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>31518 JOSE GALVEZ BARRENECHEA</t>
+          <t>ORION</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.42145</t>
+          <t>-11.41967</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.69009</t>
+          <t>-75.69093</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>291</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>245045</t>
+          <t>736982</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INDUSTRIAL 32</t>
+          <t>EINSTEIN</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.40837</t>
+          <t>-11.41969</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.68365</t>
+          <t>-75.69096</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>232</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>245050</t>
+          <t>751736</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ANGELA MORENO DE GALVEZ</t>
+          <t>NUEVO HORIZONTE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.414197</t>
+          <t>-11.42067</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.685615</t>
+          <t>-75.69427</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>234</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>245192</t>
+          <t>757922</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>PERUANO EUROPEO CELESTIN FREINET</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.4173</t>
+          <t>-11.40734</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.67931</t>
+          <t>-75.68238</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>245229</t>
+          <t>245253</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA</t>
+          <t>SANTA CLARA DE ASIS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.42046</t>
+          <t>-11.4163</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-75.69265</t>
+          <t>-75.69537</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>269</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>245253</t>
+          <t>244673</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SANTA CLARA DE ASIS</t>
+          <t>30711 WILHELM HOFMANN</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.4163</t>
+          <t>-11.41853</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.69537</t>
+          <t>-75.68477</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>245272</t>
+          <t>508433</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HUGO VELASQUEZ MACASSI</t>
+          <t>FE Y ALEGRIA 67 MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.41605</t>
+          <t>-11.41521</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.68384</t>
+          <t>-75.67847</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>366</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>245347</t>
+          <t>244588</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AGORA</t>
+          <t>SANTA TERESA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.41741</t>
+          <t>-11.42242</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.68996</t>
+          <t>-75.69277</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>523</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>245465</t>
+          <t>244965</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DE PRAGA</t>
+          <t>31517 ANGELA MORENO DE GALVEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.42182</t>
+          <t>-11.4139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.6881</t>
+          <t>-75.68609</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>407</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>246139</t>
+          <t>245229</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30731 SOR IRENE THERESE MC CORMACK</t>
+          <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.2657</t>
+          <t>-11.42046</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.6498</t>
+          <t>-75.69265</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>387</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>246894</t>
+          <t>244606</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30743 SAN ANTONIO DE PADUA / 717</t>
+          <t>30703 JOSE GUILLERMO OTERO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.295425</t>
+          <t>-11.42492</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.772823</t>
+          <t>-75.69206</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>341</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>295361</t>
+          <t>245347</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ORION</t>
+          <t>AGORA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.41967</t>
+          <t>-11.41741</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.69093</t>
+          <t>-75.68996</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>508433</t>
+          <t>244951</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 67 MARIA INMACULADA</t>
+          <t>31516 MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.41521</t>
+          <t>-11.41546</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.67847</t>
+          <t>-75.68332</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>743</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>655037</t>
+          <t>244970</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>31518 JOSE GALVEZ BARRENECHEA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.43186</t>
+          <t>-11.42145</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.69118</t>
+          <t>-75.69009</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>823</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>736982</t>
+          <t>245192</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>EINSTEIN</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.41969</t>
+          <t>-11.4173</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.69096</t>
+          <t>-75.67931</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>751736</t>
+          <t>245045</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>NUEVO HORIZONTE</t>
+          <t>INDUSTRIAL 32</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.42067</t>
+          <t>-11.40837</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.69427</t>
+          <t>-75.68365</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>976</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>757922</t>
+          <t>245050</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PERUANO EUROPEO CELESTIN FREINET</t>
+          <t>ANGELA MORENO DE GALVEZ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.40734</t>
+          <t>-11.414197</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.68238</t>
+          <t>-75.685615</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>980</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>69</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>911867</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SACO OLIVERO TARMA</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.419918</t>
+          <t>-11.40887</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.68777</t>
+          <t>-75.68295</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
@@ -511,22 +511,22 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>-11.419918</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>-75.68777</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>245272</t>
+          <t>757922</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>HUGO VELASQUEZ MACASSI</t>
+          <t>PERUANO EUROPEO CELESTIN FREINET</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.41605</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.68384</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.40734</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.68238</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>246139</t>
+          <t>751736</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30731 SOR IRENE THERESE MC CORMACK</t>
+          <t>NUEVO HORIZONTE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.2657</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.6498</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>-11.42067</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-75.69427</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>655037</t>
+          <t>736982</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NEWTON</t>
+          <t>EINSTEIN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.43186</t>
+          <t>232</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-75.69118</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>-11.41969</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-75.69096</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>244480</t>
+          <t>655037</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>NEWTON</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.41508</t>
+          <t>427</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.68375</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-11.43186</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-75.69118</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>244649</t>
+          <t>508433</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>30708 ROSA DE SANTA MARIA</t>
+          <t>FE Y ALEGRIA 67 MARIA INMACULADA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.41904</t>
+          <t>366</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.69807</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.41521</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.67847</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>246894</t>
+          <t>295361</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>30743 SAN ANTONIO DE PADUA / 717</t>
+          <t>ORION</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.295425</t>
+          <t>291</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-75.772823</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-11.41967</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-75.69093</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>245465</t>
+          <t>246894</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NIÑO JESUS DE PRAGA</t>
+          <t>30743 SAN ANTONIO DE PADUA / 717</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.42182</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.6881</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-11.295425</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.772823</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>295361</t>
+          <t>246139</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ORION</t>
+          <t>30731 SOR IRENE THERESE MC CORMACK</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.41967</t>
+          <t>430</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.69093</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>-11.2657</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.6498</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>736982</t>
+          <t>245465</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EINSTEIN</t>
+          <t>NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.41969</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.69096</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>-11.42182</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.6881</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>751736</t>
+          <t>245347</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NUEVO HORIZONTE</t>
+          <t>AGORA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.42067</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.69427</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-11.41741</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.68996</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>757922</t>
+          <t>245272</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PERUANO EUROPEO CELESTIN FREINET</t>
+          <t>HUGO VELASQUEZ MACASSI</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.40734</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.68238</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.41605</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.68384</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1255,22 +1255,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>-11.4163</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>-75.69537</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>244673</t>
+          <t>245229</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>30711 WILHELM HOFMANN</t>
+          <t>LA SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.41853</t>
+          <t>387</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-75.68477</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>-11.42046</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.69265</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>508433</t>
+          <t>245192</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 67 MARIA INMACULADA</t>
+          <t>SAN VICENTE DE PAUL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.41521</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.67847</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>-11.4173</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-75.67931</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>244588</t>
+          <t>245050</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SANTA TERESA</t>
+          <t>ANGELA MORENO DE GALVEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.42242</t>
+          <t>980</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-75.69277</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>-11.414197</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.685615</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>244965</t>
+          <t>245045</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>31517 ANGELA MORENO DE GALVEZ</t>
+          <t>INDUSTRIAL 32</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.4139</t>
+          <t>976</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.68609</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>-11.40837</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.68365</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>245229</t>
+          <t>244970</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA</t>
+          <t>31518 JOSE GALVEZ BARRENECHEA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.42046</t>
+          <t>823</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.69265</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>-11.42145</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-75.69009</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>244606</t>
+          <t>244965</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>30703 JOSE GUILLERMO OTERO</t>
+          <t>31517 ANGELA MORENO DE GALVEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.42492</t>
+          <t>407</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-75.69206</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>-11.4139</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-75.68609</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>245347</t>
+          <t>244951</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AGORA</t>
+          <t>31516 MARISCAL CASTILLA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.41741</t>
+          <t>743</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-75.68996</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-11.41546</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-75.68332</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>244951</t>
+          <t>244673</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31516 MARISCAL CASTILLA</t>
+          <t>30711 WILHELM HOFMANN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.41546</t>
+          <t>357</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-75.68332</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>-11.41853</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-75.68477</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>244970</t>
+          <t>244649</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31518 JOSE GALVEZ BARRENECHEA</t>
+          <t>30708 ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.42145</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-75.69009</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>-11.41904</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-75.69807</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>245192</t>
+          <t>244625</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SAN VICENTE DE PAUL</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.4173</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-75.67931</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>-11.40887</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-75.68295</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>245045</t>
+          <t>244606</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>INDUSTRIAL 32</t>
+          <t>30703 JOSE GUILLERMO OTERO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.40837</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-75.68365</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>-11.42492</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-75.69206</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>245050</t>
+          <t>244588</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ANGELA MORENO DE GALVEZ</t>
+          <t>SANTA TERESA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.414197</t>
+          <t>523</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-75.685615</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>-11.42242</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-75.69277</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>244625</t>
+          <t>244480</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>202</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-11.40887</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-75.68295</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>-11.41508</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-75.68375</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">

--- a/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
+++ b/ZonasEscolares/excels/JUNIN-TARMA-TARMA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
